--- a/output/table_14_oecd_oda_breakdown.xlsx
+++ b/output/table_14_oecd_oda_breakdown.xlsx
@@ -858,38 +858,38 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Other Multilaterals</t>
+          <t>Others</t>
         </is>
       </c>
       <c r="B14">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="C14">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="E14">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="F14">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="G14">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="H14">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="I14">
-        <v>11.7</v>
+        <v>11.1</v>
       </c>
       <c r="J14">
-        <v>18</v>
+        <v>16.3</v>
       </c>
       <c r="K14">
-        <v>10.5</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="15">

--- a/output/table_14_oecd_oda_breakdown.xlsx
+++ b/output/table_14_oecd_oda_breakdown.xlsx
@@ -482,7 +482,7 @@
         <v>165.1</v>
       </c>
       <c r="K3">
-        <v>160.5</v>
+        <v>160.6</v>
       </c>
     </row>
     <row r="4">
@@ -519,7 +519,7 @@
         <v>18.8</v>
       </c>
       <c r="K4">
-        <v>17.7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -926,7 +926,7 @@
         <v>31.3</v>
       </c>
       <c r="K15">
-        <v>30</v>
+        <v>30.4</v>
       </c>
     </row>
   </sheetData>
